--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484115_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484115_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4745</v>
+        <v>4.3836</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4846</v>
+        <v>3.0571</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9899</v>
+        <v>1.3266</v>
       </c>
       <c r="G2" t="n">
         <v>-0.016</v>
@@ -610,13 +610,13 @@
         <v>4.7612</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.8306</v>
+        <v>-1.9215</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.4226</v>
+        <v>-0.8501</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.408</v>
+        <v>-1.0714</v>
       </c>
       <c r="V2" t="n">
         <v>2.7502</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4807</v>
+        <v>2.28</v>
       </c>
       <c r="E3" t="n">
-        <v>3.239</v>
+        <v>2.8138</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7583</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>2.3621</v>
@@ -688,13 +688,13 @@
         <v>3.3725</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4171</v>
+        <v>-0.6178</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1872</v>
+        <v>-0.238</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6042999999999999</v>
+        <v>-0.3798</v>
       </c>
       <c r="V3" t="n">
         <v>0.3373</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6972</v>
+        <v>1.2158</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7609</v>
+        <v>1.5602</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0638</v>
+        <v>-0.3443</v>
       </c>
       <c r="G4" t="n">
         <v>0.7689</v>
@@ -766,13 +766,13 @@
         <v>4.7612</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.528</v>
+        <v>-2.0093</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.7457</v>
+        <v>-0.9465</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7823</v>
+        <v>-1.0629</v>
       </c>
       <c r="V4" t="n">
         <v>0.8692</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0111</v>
+        <v>0.2031</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1796</v>
+        <v>0.2816</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1907</v>
+        <v>-0.0785</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4256</v>
@@ -844,13 +844,13 @@
         <v>0.3968</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2483</v>
+        <v>-0.034</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.187</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0612</v>
+        <v>0.051</v>
       </c>
       <c r="V5" t="n">
         <v>0.266</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-0.2096</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.369</v>
+        <v>-2.1649</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8151</v>
+        <v>1.9554</v>
       </c>
       <c r="G6" t="n">
         <v>-0.7948</v>
@@ -922,13 +922,13 @@
         <v>2.3806</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1478</v>
+        <v>-0.8034</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4251</v>
+        <v>-0.221</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7227</v>
+        <v>-0.5824</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.742</v>
+        <v>-0.3977</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2865</v>
+        <v>1.4906</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.0286</v>
+        <v>-1.8883</v>
       </c>
       <c r="G7" t="n">
         <v>-2.9117</v>
@@ -1000,13 +1000,13 @@
         <v>2.3806</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1478</v>
+        <v>-0.8034</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9352</v>
+        <v>-0.7311</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2126</v>
+        <v>-0.0723</v>
       </c>
       <c r="V7" t="n">
         <v>1.1352</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5215</v>
+        <v>-1.3634</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5493</v>
+        <v>-1.4473</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0277</v>
+        <v>0.0839</v>
       </c>
       <c r="G8" t="n">
         <v>-2.0294</v>
@@ -1078,13 +1078,13 @@
         <v>0.9919</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4841</v>
+        <v>-0.3259</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2494</v>
+        <v>-0.1474</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2347</v>
+        <v>-0.1786</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. ESONO MBA</t>
+          <t>J. SERRA ANGLÈS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6199</v>
+        <v>-2.5609</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6206</v>
+        <v>-2.2679</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9993</v>
+        <v>-0.2929</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.8546</v>
+        <v>-2.9278</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0202</v>
+        <v>-1.0026</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.8344</v>
+        <v>-1.9252</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1161</v>
+        <v>-1.2818</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0446</v>
+        <v>-0.6845</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1606</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9707</v>
+        <v>-1.646</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0244</v>
+        <v>-0.3181</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.9951</v>
+        <v>-1.3279</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.7693</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9838</v>
+        <v>3.7693</v>
       </c>
       <c r="S9" t="n">
-        <v>2.6476</v>
+        <v>-1.2555</v>
       </c>
       <c r="T9" t="n">
-        <v>1.9216</v>
+        <v>-0.3117</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7259</v>
+        <v>-0.9438</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.4129</v>
+        <v>-2.1469</v>
       </c>
       <c r="W9" t="n">
         <v>-0.6745</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.7384</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. SERRA ANGLÈS</t>
+          <t>J. ESONO MBA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5284</v>
+        <v>-3.671</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0671</v>
+        <v>-2.0264</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4613</v>
+        <v>-1.6446</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.9278</v>
+        <v>-1.8546</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0026</v>
+        <v>-0.0202</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.9252</v>
+        <v>-1.8344</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2818</v>
+        <v>0.1161</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6845</v>
+        <v>-0.0446</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5973000000000001</v>
+        <v>0.1606</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.646</v>
+        <v>-1.9707</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3181</v>
+        <v>0.0244</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3279</v>
+        <v>-1.9951</v>
       </c>
       <c r="P10" t="n">
-        <v>3.7693</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R10" t="n">
-        <v>3.7693</v>
+        <v>1.9838</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.223</v>
+        <v>0.5966</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1109</v>
+        <v>0.5159</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1121</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1469</v>
+        <v>-2.4129</v>
       </c>
       <c r="W10" t="n">
         <v>-0.6745</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4724</v>
+        <v>-1.7384</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.3064</v>
+        <v>-7.576</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.948</v>
+        <v>-3.965</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.3585</v>
+        <v>-3.611</v>
       </c>
       <c r="G11" t="n">
         <v>-4.9973</v>
@@ -1312,13 +1312,13 @@
         <v>2.9758</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6898</v>
+        <v>-0.9593</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5667</v>
+        <v>-0.5837</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1231</v>
+        <v>-0.3756</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4129</v>
@@ -1345,37 +1345,37 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.630800000000001</v>
+        <v>-7.696099999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.603400000000001</v>
+        <v>-2.668199999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.0278</v>
+        <v>-5.0275</v>
       </c>
       <c r="G12" t="n">
         <v>-12.8262</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0001999999999997559</v>
+        <v>-0.0001999999999990898</v>
       </c>
       <c r="I12" t="n">
         <v>-12.8262</v>
       </c>
       <c r="J12" t="n">
-        <v>9.0183</v>
+        <v>9.018299999999998</v>
       </c>
       <c r="K12" t="n">
         <v>5.877400000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>3.1409</v>
+        <v>3.140899999999999</v>
       </c>
       <c r="M12" t="n">
         <v>-21.8447</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.877500000000001</v>
+        <v>-5.8775</v>
       </c>
       <c r="O12" t="n">
         <v>-15.967</v>
@@ -1387,13 +1387,13 @@
         <v>-12.8948</v>
       </c>
       <c r="R12" t="n">
-        <v>27.7737</v>
+        <v>27.77369999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-9.068900000000001</v>
+        <v>-8.1335</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.5338</v>
+        <v>-3.5986</v>
       </c>
       <c r="U12" t="n">
         <v>-4.5351</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.392200000000001</v>
+        <v>7.6092</v>
       </c>
       <c r="E13" t="n">
-        <v>6.8148</v>
+        <v>6.5087</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5774</v>
+        <v>1.1004</v>
       </c>
       <c r="G13" t="n">
         <v>7.0122</v>
@@ -1468,13 +1468,13 @@
         <v>2.1822</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1735</v>
+        <v>2.3905</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4908</v>
+        <v>1.1847</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6827</v>
+        <v>1.2057</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6032</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. MARTINEZ YRANZO</t>
+          <t>L. MALARY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7353</v>
+        <v>3.1251</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2338</v>
+        <v>4.3885</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5015</v>
+        <v>-1.2634</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8179</v>
+        <v>2.3834</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.781</v>
+        <v>3.7399</v>
       </c>
       <c r="I14" t="n">
-        <v>2.5989</v>
+        <v>-1.3564</v>
       </c>
       <c r="J14" t="n">
-        <v>2.5739</v>
+        <v>4.5687</v>
       </c>
       <c r="K14" t="n">
-        <v>0.001</v>
+        <v>5.0054</v>
       </c>
       <c r="L14" t="n">
-        <v>2.5729</v>
+        <v>-0.4367</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.756</v>
+        <v>-2.1853</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.782</v>
+        <v>-1.2655</v>
       </c>
       <c r="O14" t="n">
-        <v>0.026</v>
+        <v>-0.9198</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q14" t="n">
-        <v>-5.158</v>
+        <v>-2.1822</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1822</v>
+        <v>1.1903</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9483</v>
+        <v>0.5271</v>
       </c>
       <c r="T14" t="n">
-        <v>0.873</v>
+        <v>-0.0736</v>
       </c>
       <c r="U14" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.6008</v>
       </c>
       <c r="V14" t="n">
-        <v>2.9449</v>
+        <v>1.2065</v>
       </c>
       <c r="W14" t="n">
-        <v>2.9449</v>
+        <v>2.0757</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. MALARY</t>
+          <t>L. MARTINEZ YRANZO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6252</v>
+        <v>3.0779</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7764</v>
+        <v>1.1318</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1512</v>
+        <v>1.9461</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3834</v>
+        <v>1.8179</v>
       </c>
       <c r="H15" t="n">
-        <v>3.7399</v>
+        <v>-0.781</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.3564</v>
+        <v>2.5989</v>
       </c>
       <c r="J15" t="n">
-        <v>4.5687</v>
+        <v>2.5739</v>
       </c>
       <c r="K15" t="n">
-        <v>5.0054</v>
+        <v>0.001</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.4367</v>
+        <v>2.5729</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.1853</v>
+        <v>-0.756</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2655</v>
+        <v>-0.782</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9198</v>
+        <v>0.026</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9919</v>
+        <v>-2.9758</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1822</v>
+        <v>-5.158</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1903</v>
+        <v>2.1822</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0272</v>
+        <v>1.2909</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6858</v>
+        <v>0.7709</v>
       </c>
       <c r="U15" t="n">
-        <v>0.713</v>
+        <v>0.5199</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2065</v>
+        <v>2.9449</v>
       </c>
       <c r="W15" t="n">
-        <v>2.0757</v>
+        <v>2.9449</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8692</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4596</v>
+        <v>0.4428</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6338</v>
+        <v>-1.4501</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0934</v>
+        <v>1.8928</v>
       </c>
       <c r="G16" t="n">
         <v>-0.0678</v>
@@ -1702,13 +1702,13 @@
         <v>0.5952</v>
       </c>
       <c r="S16" t="n">
-        <v>1.714</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>0.924</v>
+        <v>0.1077</v>
       </c>
       <c r="U16" t="n">
-        <v>0.79</v>
+        <v>0.5894</v>
       </c>
       <c r="V16" t="n">
         <v>0.4085</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3292</v>
+        <v>0.2915</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7244</v>
+        <v>-0.5203</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3952</v>
+        <v>0.8118</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4425</v>
@@ -1780,13 +1780,13 @@
         <v>0.3968</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2834</v>
+        <v>0.3372</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1247</v>
+        <v>0.0794</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1587</v>
+        <v>0.2579</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. COFFIE</t>
+          <t>A. CASTILLO EDIO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6601</v>
+        <v>-0.0061</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8648</v>
+        <v>1.3686</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2047</v>
+        <v>-1.3747</v>
       </c>
       <c r="G18" t="n">
-        <v>2.3961</v>
+        <v>2.9364</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4062</v>
+        <v>-0.4943</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9899</v>
+        <v>3.4307</v>
       </c>
       <c r="J18" t="n">
-        <v>4.0947</v>
+        <v>4.1629</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9259</v>
+        <v>0.2271</v>
       </c>
       <c r="L18" t="n">
-        <v>2.1687</v>
+        <v>3.9358</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6986</v>
+        <v>-1.2265</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1788</v>
+        <v>-0.5051</v>
       </c>
       <c r="P18" t="n">
-        <v>-3.5709</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q18" t="n">
-        <v>-5.158</v>
+        <v>-3.3725</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5871</v>
+        <v>2.1822</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1892</v>
+        <v>0.9267</v>
       </c>
       <c r="T18" t="n">
-        <v>0.873</v>
+        <v>0.5782</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3162</v>
+        <v>0.3485</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6745</v>
+        <v>-2.6789</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6745</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.6789</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. CASTILLO EDIO</t>
+          <t>D. COFFIE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6845</v>
+        <v>-0.4918</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8585</v>
+        <v>-0.8648</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.543</v>
+        <v>0.373</v>
       </c>
       <c r="G19" t="n">
-        <v>2.9364</v>
+        <v>2.3961</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4943</v>
+        <v>1.4062</v>
       </c>
       <c r="I19" t="n">
-        <v>3.4307</v>
+        <v>0.9899</v>
       </c>
       <c r="J19" t="n">
-        <v>4.1629</v>
+        <v>4.0947</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2271</v>
+        <v>1.9259</v>
       </c>
       <c r="L19" t="n">
-        <v>3.9358</v>
+        <v>2.1687</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2265</v>
+        <v>-1.6986</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5051</v>
+        <v>-1.1788</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1903</v>
+        <v>-3.5709</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.3725</v>
+        <v>-5.158</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1822</v>
+        <v>1.5871</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2483</v>
+        <v>1.3575</v>
       </c>
       <c r="T19" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.873</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1802</v>
+        <v>0.4845</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.6789</v>
+        <v>-0.6745</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.6789</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V. CEBRIA PUCHADES</t>
+          <t>J. ROSA DE SOUSA DA SILVA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8509</v>
+        <v>-0.6304</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8333</v>
+        <v>-0.4718</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9824000000000001</v>
+        <v>-0.1586</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.9603</v>
+        <v>-0.0304</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.7891</v>
+        <v>-1.6032</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1712</v>
+        <v>1.5728</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.26</v>
+        <v>0.8091</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.9398</v>
+        <v>-0.4786</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3202</v>
+        <v>1.2877</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2997</v>
+        <v>-0.8395</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1507</v>
+        <v>-1.1246</v>
       </c>
       <c r="O20" t="n">
-        <v>0.149</v>
+        <v>0.2851</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.7855</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9758</v>
+        <v>-1.1903</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1903</v>
+        <v>0.9919</v>
       </c>
       <c r="S20" t="n">
-        <v>2.0139</v>
+        <v>0.4676</v>
       </c>
       <c r="T20" t="n">
-        <v>1.9896</v>
+        <v>-0.0906</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0243</v>
+        <v>0.5582</v>
       </c>
       <c r="V20" t="n">
-        <v>1.881</v>
+        <v>-0.8692</v>
       </c>
       <c r="W20" t="n">
-        <v>2.4129</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.532</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2291</v>
+        <v>-1.201</v>
       </c>
       <c r="E21" t="n">
         <v>-1.1166</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1125</v>
+        <v>-0.0844</v>
       </c>
       <c r="G21" t="n">
         <v>0.0049</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.242</v>
+        <v>-0.214</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1247</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1173</v>
+        <v>-0.0893</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. ROSA DE SOUSA DA SILVA</t>
+          <t>H. RAMON AÑIBARRO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3428</v>
+        <v>-1.3008</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8799</v>
+        <v>-1.1948</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4629</v>
+        <v>-0.106</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0304</v>
+        <v>-0.2238</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6032</v>
+        <v>0.5794</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5728</v>
+        <v>-0.8032</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8091</v>
+        <v>0.8287</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4786</v>
+        <v>0.7057</v>
       </c>
       <c r="L22" t="n">
-        <v>1.2877</v>
+        <v>0.123</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8395</v>
+        <v>-1.0525</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1246</v>
+        <v>-0.1263</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2851</v>
+        <v>-0.9263</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1984</v>
+        <v>-1.7855</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1903</v>
+        <v>-2.1822</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9919</v>
+        <v>0.3968</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2449</v>
+        <v>0.7085</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4988</v>
+        <v>0.1587</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2539</v>
+        <v>0.5498</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.8692</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8692</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>H. RAMON AÑIBARRO</t>
+          <t>V. CEBRIA PUCHADES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4845</v>
+        <v>-1.605</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6029</v>
+        <v>-2.7515</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1184</v>
+        <v>1.1465</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2238</v>
+        <v>-2.9603</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5794</v>
+        <v>-1.7891</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8032</v>
+        <v>-1.1712</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8287</v>
+        <v>-3.26</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7057</v>
+        <v>-1.9398</v>
       </c>
       <c r="L23" t="n">
-        <v>0.123</v>
+        <v>-1.3202</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0525</v>
+        <v>0.2997</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1263</v>
+        <v>0.1507</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9263</v>
+        <v>0.149</v>
       </c>
       <c r="P23" t="n">
         <v>-1.7855</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1822</v>
+        <v>-2.9758</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3968</v>
+        <v>1.1903</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5248</v>
+        <v>1.2597</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2494</v>
+        <v>1.0713</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7742</v>
+        <v>0.1884</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.881</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.4129</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="24">
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>8.631199999999998</v>
+        <v>9.311399999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>5.0278</v>
+        <v>5.027699999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>3.6034</v>
+        <v>4.2835</v>
       </c>
       <c r="G24" t="n">
         <v>12.8261</v>
       </c>
       <c r="H24" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>12.8263</v>
@@ -2311,7 +2311,7 @@
         <v>-9.0185</v>
       </c>
       <c r="N24" t="n">
-        <v>-5.877399999999999</v>
+        <v>-5.877400000000001</v>
       </c>
       <c r="O24" t="n">
         <v>-3.141</v>
@@ -2320,19 +2320,19 @@
         <v>-14.8789</v>
       </c>
       <c r="Q24" t="n">
-        <v>-27.7737</v>
+        <v>-27.77370000000001</v>
       </c>
       <c r="R24" t="n">
         <v>12.895</v>
       </c>
       <c r="S24" t="n">
-        <v>9.068900000000003</v>
+        <v>9.748800000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>4.5351</v>
+        <v>4.535</v>
       </c>
       <c r="U24" t="n">
-        <v>4.533799999999999</v>
+        <v>5.2138</v>
       </c>
       <c r="V24" t="n">
         <v>1.6151</v>
